--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D218F6B1-6E39-9C42-88F2-FED1B27174BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7599697B-CBAA-AD42-BD52-D2FA58CB2900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3132" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:DX32"/>
+  <dimension ref="A1:DY32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:128" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:129" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1031,18 +1031,21 @@
       <c r="DX1" s="3">
         <v>46078</v>
       </c>
+      <c r="DY1" s="3">
+        <v>46079</v>
+      </c>
     </row>
-    <row r="2" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1426,14 +1429,17 @@
       <c r="DX2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -1457,7 +1463,7 @@
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H26" si="6">COUNTIF(K3:VV3,"R")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I26" si="7">COUNTIF(K3:VW3,"RH")</f>
@@ -1821,18 +1827,21 @@
       <c r="DX3" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="DY3" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2216,18 +2225,21 @@
       <c r="DX4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2611,14 +2623,17 @@
       <c r="DX5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
@@ -2634,7 +2649,7 @@
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(K6:VT6,"B")</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="5"/>
@@ -3006,18 +3021,21 @@
       <c r="DX6" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="DY6" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="7" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3401,14 +3419,17 @@
       <c r="DX7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY7" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -3424,7 +3445,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -3796,18 +3817,21 @@
       <c r="DX8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="DY8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4191,18 +4215,21 @@
       <c r="DX9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -4586,18 +4613,21 @@
       <c r="DX10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -4981,8 +5011,11 @@
       <c r="DX11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5143,13 +5176,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -5165,7 +5198,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -5537,18 +5570,21 @@
       <c r="DX13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="DY13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -5932,18 +5968,21 @@
       <c r="DX14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -6327,8 +6366,11 @@
       <c r="DX15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -6690,8 +6732,9 @@
       <c r="DV16" s="4"/>
       <c r="DW16" s="4"/>
       <c r="DX16" s="4"/>
+      <c r="DY16" s="4"/>
     </row>
-    <row r="17" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7039,18 +7082,19 @@
       <c r="DV17" s="4"/>
       <c r="DW17" s="4"/>
       <c r="DX17" s="4"/>
+      <c r="DY17" s="4"/>
     </row>
-    <row r="18" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -7434,18 +7478,21 @@
       <c r="DX18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -7829,18 +7876,21 @@
       <c r="DX19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="4"/>
@@ -8224,8 +8274,11 @@
       <c r="DX20" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY20" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -8471,17 +8524,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -8865,8 +8918,11 @@
       <c r="DX22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -9168,17 +9224,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -9562,8 +9618,11 @@
       <c r="DX24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -9913,18 +9972,19 @@
       <c r="DV25" s="4"/>
       <c r="DW25" s="4"/>
       <c r="DX25" s="4"/>
+      <c r="DY25" s="4"/>
     </row>
-    <row r="26" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -10308,18 +10368,21 @@
       <c r="DX26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -10673,18 +10736,21 @@
       <c r="DX27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B28" s="4">
         <f t="shared" si="11"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C28" s="4">
         <f t="shared" si="12"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" si="13"/>
@@ -10972,18 +11038,21 @@
       <c r="DX28" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY28" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -11271,18 +11340,21 @@
       <c r="DX29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -11405,18 +11477,21 @@
       <c r="DX30" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY30" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -11503,18 +11578,21 @@
       <c r="DX31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DY31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:128" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:129" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -11587,6 +11665,9 @@
         <v>7</v>
       </c>
       <c r="DX32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="DY32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7599697B-CBAA-AD42-BD52-D2FA58CB2900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3C1AAD-FD23-854E-83C5-42F915ECDBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3132" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3182" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:DY32"/>
+  <dimension ref="A1:EA32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:129" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:131" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1034,18 +1034,24 @@
       <c r="DY1" s="3">
         <v>46079</v>
       </c>
+      <c r="DZ1" s="3">
+        <v>46084</v>
+      </c>
+      <c r="EA1" s="3">
+        <v>46085</v>
+      </c>
     </row>
-    <row r="2" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1432,18 +1438,24 @@
       <c r="DY2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D3" s="6">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1830,18 +1842,24 @@
       <c r="DY3" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="DZ3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA3" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2228,18 +2246,24 @@
       <c r="DY4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2626,14 +2650,20 @@
       <c r="DY5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
@@ -2661,7 +2691,7 @@
       </c>
       <c r="I6" s="4">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="8"/>
@@ -3024,18 +3054,24 @@
       <c r="DY6" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="DZ6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="EA6" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="7" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3422,14 +3458,20 @@
       <c r="DY7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA7" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -3445,7 +3487,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -3820,18 +3862,24 @@
       <c r="DY8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="DZ8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EA8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4218,18 +4266,24 @@
       <c r="DY9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -4616,18 +4670,24 @@
       <c r="DY10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5014,8 +5074,14 @@
       <c r="DY11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5176,13 +5242,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -5198,7 +5264,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -5573,18 +5639,24 @@
       <c r="DY13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="DZ13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EA13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -5971,14 +6043,20 @@
       <c r="DY14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
@@ -5994,7 +6072,7 @@
       </c>
       <c r="F15" s="4">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="5"/>
@@ -6369,8 +6447,14 @@
       <c r="DY15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EA15" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="16" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -6733,8 +6817,10 @@
       <c r="DW16" s="4"/>
       <c r="DX16" s="4"/>
       <c r="DY16" s="4"/>
+      <c r="DZ16" s="4"/>
+      <c r="EA16" s="4"/>
     </row>
-    <row r="17" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7083,18 +7169,20 @@
       <c r="DW17" s="4"/>
       <c r="DX17" s="4"/>
       <c r="DY17" s="4"/>
+      <c r="DZ17" s="4"/>
+      <c r="EA17" s="4"/>
     </row>
-    <row r="18" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -7481,14 +7569,20 @@
       <c r="DY18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
@@ -7504,7 +7598,7 @@
       </c>
       <c r="F19" s="4">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="5"/>
@@ -7879,18 +7973,24 @@
       <c r="DY19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EA19" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="20" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="4"/>
@@ -8277,8 +8377,14 @@
       <c r="DY20" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA20" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -8524,17 +8630,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -8921,8 +9027,14 @@
       <c r="DY22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -9224,17 +9336,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -9621,8 +9733,14 @@
       <c r="DY24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -9973,18 +10091,20 @@
       <c r="DW25" s="4"/>
       <c r="DX25" s="4"/>
       <c r="DY25" s="4"/>
+      <c r="DZ25" s="4"/>
+      <c r="EA25" s="4"/>
     </row>
-    <row r="26" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -10371,18 +10491,24 @@
       <c r="DY26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -10739,18 +10865,24 @@
       <c r="DY27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B28" s="4">
         <f t="shared" si="11"/>
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C28" s="4">
         <f t="shared" si="12"/>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" si="13"/>
@@ -11041,18 +11173,24 @@
       <c r="DY28" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA28" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -11343,18 +11481,24 @@
       <c r="DY29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -11480,18 +11624,24 @@
       <c r="DY30" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA30" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -11581,18 +11731,24 @@
       <c r="DY31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="DZ31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:131" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -11668,6 +11824,12 @@
         <v>7</v>
       </c>
       <c r="DY32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="DZ32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3C1AAD-FD23-854E-83C5-42F915ECDBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE9FA12-19E6-AE41-8606-7B9919CC14C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3182" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3207" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:EA32"/>
+  <dimension ref="A1:EB32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:131" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:132" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1040,18 +1040,21 @@
       <c r="EA1" s="3">
         <v>46085</v>
       </c>
+      <c r="EB1" s="3">
+        <v>46087</v>
+      </c>
     </row>
-    <row r="2" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1444,14 +1447,17 @@
       <c r="EA2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -1475,7 +1481,7 @@
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H26" si="6">COUNTIF(K3:VV3,"R")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I26" si="7">COUNTIF(K3:VW3,"RH")</f>
@@ -1848,18 +1854,21 @@
       <c r="EA3" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB3" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2252,18 +2261,21 @@
       <c r="EA4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2656,14 +2668,17 @@
       <c r="EA5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
@@ -2691,7 +2706,7 @@
       </c>
       <c r="I6" s="4">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="8"/>
@@ -3060,18 +3075,21 @@
       <c r="EA6" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="EB6" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="7" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3464,14 +3482,17 @@
       <c r="EA7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB7" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -3487,7 +3508,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -3868,18 +3889,21 @@
       <c r="EA8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EB8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4272,18 +4296,21 @@
       <c r="EA9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -4676,18 +4703,21 @@
       <c r="EA10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5080,8 +5110,11 @@
       <c r="EA11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5242,13 +5275,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -5264,7 +5297,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -5645,18 +5678,21 @@
       <c r="EA13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EB13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6049,14 +6085,17 @@
       <c r="EA14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
@@ -6072,7 +6111,7 @@
       </c>
       <c r="F15" s="4">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="5"/>
@@ -6453,8 +6492,11 @@
       <c r="EA15" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EB15" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="16" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -6819,8 +6861,9 @@
       <c r="DY16" s="4"/>
       <c r="DZ16" s="4"/>
       <c r="EA16" s="4"/>
+      <c r="EB16" s="4"/>
     </row>
-    <row r="17" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7171,18 +7214,19 @@
       <c r="DY17" s="4"/>
       <c r="DZ17" s="4"/>
       <c r="EA17" s="4"/>
+      <c r="EB17" s="4"/>
     </row>
-    <row r="18" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -7575,14 +7619,17 @@
       <c r="EA18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
@@ -7598,7 +7645,7 @@
       </c>
       <c r="F19" s="4">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="5"/>
@@ -7979,18 +8026,21 @@
       <c r="EA19" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EB19" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="20" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="4"/>
@@ -8383,8 +8433,11 @@
       <c r="EA20" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB20" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -8630,17 +8683,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -9033,8 +9086,11 @@
       <c r="EA22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -9336,17 +9392,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -9739,8 +9795,11 @@
       <c r="EA24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -10093,18 +10152,19 @@
       <c r="DY25" s="4"/>
       <c r="DZ25" s="4"/>
       <c r="EA25" s="4"/>
+      <c r="EB25" s="4"/>
     </row>
-    <row r="26" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -10497,18 +10557,21 @@
       <c r="EA26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -10871,18 +10934,21 @@
       <c r="EA27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B28" s="4">
         <f t="shared" si="11"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C28" s="4">
         <f t="shared" si="12"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" si="13"/>
@@ -11179,18 +11245,21 @@
       <c r="EA28" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB28" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -11487,18 +11556,21 @@
       <c r="EA29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -11630,18 +11702,21 @@
       <c r="EA30" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB30" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -11737,18 +11812,21 @@
       <c r="EA31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EB31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:132" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -11830,6 +11908,9 @@
         <v>7</v>
       </c>
       <c r="EA32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EB32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE9FA12-19E6-AE41-8606-7B9919CC14C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172CA0FA-0370-4147-BF97-9122944652FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3207" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3257" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:EB32"/>
+  <dimension ref="A1:ED32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:132" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:134" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1043,18 +1043,24 @@
       <c r="EB1" s="3">
         <v>46087</v>
       </c>
+      <c r="EC1" s="3">
+        <v>46091</v>
+      </c>
+      <c r="ED1" s="3">
+        <v>46092</v>
+      </c>
     </row>
-    <row r="2" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1450,18 +1456,24 @@
       <c r="EB2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D3" s="6">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1857,18 +1869,24 @@
       <c r="EB3" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="EC3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED3" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2264,18 +2282,24 @@
       <c r="EB4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2671,18 +2695,24 @@
       <c r="EB5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="4"/>
@@ -3078,18 +3108,24 @@
       <c r="EB6" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="EC6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED6" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3101,7 +3137,7 @@
       </c>
       <c r="F7" s="4">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="5"/>
@@ -3485,14 +3521,20 @@
       <c r="EB7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED7" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="8" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -3520,7 +3562,7 @@
       </c>
       <c r="I8" s="4">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="8"/>
@@ -3892,18 +3934,24 @@
       <c r="EB8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EC8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="ED8" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="9" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4299,18 +4347,24 @@
       <c r="EB9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -4706,18 +4760,24 @@
       <c r="EB10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5113,8 +5173,14 @@
       <c r="EB11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5275,13 +5341,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -5297,7 +5363,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -5681,18 +5747,24 @@
       <c r="EB13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EC13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="ED13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6088,18 +6160,24 @@
       <c r="EB14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -6495,8 +6573,14 @@
       <c r="EB15" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EC15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -6862,8 +6946,10 @@
       <c r="DZ16" s="4"/>
       <c r="EA16" s="4"/>
       <c r="EB16" s="4"/>
+      <c r="EC16" s="4"/>
+      <c r="ED16" s="4"/>
     </row>
-    <row r="17" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7215,18 +7301,20 @@
       <c r="DZ17" s="4"/>
       <c r="EA17" s="4"/>
       <c r="EB17" s="4"/>
+      <c r="EC17" s="4"/>
+      <c r="ED17" s="4"/>
     </row>
-    <row r="18" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -7622,18 +7710,24 @@
       <c r="EB18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -8029,18 +8123,24 @@
       <c r="EB19" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EC19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="4"/>
@@ -8436,8 +8536,14 @@
       <c r="EB20" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED20" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -8683,17 +8789,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -9089,8 +9195,14 @@
       <c r="EB22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -9392,17 +9504,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -9798,8 +9910,14 @@
       <c r="EB24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -10153,18 +10271,20 @@
       <c r="DZ25" s="4"/>
       <c r="EA25" s="4"/>
       <c r="EB25" s="4"/>
+      <c r="EC25" s="4"/>
+      <c r="ED25" s="4"/>
     </row>
-    <row r="26" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -10560,18 +10680,24 @@
       <c r="EB26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -10937,18 +11063,24 @@
       <c r="EB27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B28" s="4">
         <f t="shared" si="11"/>
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C28" s="4">
         <f t="shared" si="12"/>
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" si="13"/>
@@ -11248,18 +11380,24 @@
       <c r="EB28" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED28" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -11559,18 +11697,24 @@
       <c r="EB29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -11705,18 +11849,24 @@
       <c r="EB30" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED30" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -11732,7 +11882,7 @@
       </c>
       <c r="G31" s="4">
         <f t="shared" ref="G31" si="34">COUNTIF(K31:VU31,"M")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31" si="35">COUNTIF(K31:VV31,"R")</f>
@@ -11815,18 +11965,24 @@
       <c r="EB31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EC31" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="ED31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:132" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -11834,7 +11990,7 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" ref="E32" si="41">COUNTIF(K32:VS32,"A")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" ref="F32" si="42">COUNTIF(K32:VT32,"B")</f>
@@ -11911,6 +12067,12 @@
         <v>7</v>
       </c>
       <c r="EB32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EC32" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="ED32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172CA0FA-0370-4147-BF97-9122944652FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A7ABFB-CDC4-1843-B93A-B48F163359DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3257" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3357" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:ED32"/>
+  <dimension ref="A1:EH32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:134" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:138" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1049,18 +1049,30 @@
       <c r="ED1" s="3">
         <v>46092</v>
       </c>
+      <c r="EE1" s="3">
+        <v>46093</v>
+      </c>
+      <c r="EF1" s="3">
+        <v>46097</v>
+      </c>
+      <c r="EG1" s="3">
+        <v>46098</v>
+      </c>
+      <c r="EH1" s="3">
+        <v>46099</v>
+      </c>
     </row>
-    <row r="2" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1462,18 +1474,30 @@
       <c r="ED2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D3" s="6">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1875,18 +1899,30 @@
       <c r="ED3" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH3" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2288,18 +2324,30 @@
       <c r="ED4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2701,18 +2749,30 @@
       <c r="ED5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="4"/>
@@ -2720,7 +2780,7 @@
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(K6:VT6,"B")</f>
@@ -2732,7 +2792,7 @@
       </c>
       <c r="H6" s="4">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="7"/>
@@ -3114,14 +3174,26 @@
       <c r="ED6" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="EF6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="EG6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="EH6" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
@@ -3137,7 +3209,7 @@
       </c>
       <c r="F7" s="4">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="5"/>
@@ -3527,18 +3599,30 @@
       <c r="ED7" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EE7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EF7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EG7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EH7" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="8" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" si="4"/>
@@ -3562,7 +3646,7 @@
       </c>
       <c r="I8" s="4">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="8"/>
@@ -3940,18 +4024,30 @@
       <c r="ED8" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="EE8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="EF8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH8" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4353,18 +4449,30 @@
       <c r="ED9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -4766,18 +4874,30 @@
       <c r="ED10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5179,8 +5299,20 @@
       <c r="ED11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5341,13 +5473,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -5363,7 +5495,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -5753,18 +5885,30 @@
       <c r="ED13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EE13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EF13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EG13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EH13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6166,18 +6310,30 @@
       <c r="ED14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -6579,8 +6735,20 @@
       <c r="ED15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -6948,8 +7116,12 @@
       <c r="EB16" s="4"/>
       <c r="EC16" s="4"/>
       <c r="ED16" s="4"/>
+      <c r="EE16" s="4"/>
+      <c r="EF16" s="4"/>
+      <c r="EG16" s="4"/>
+      <c r="EH16" s="4"/>
     </row>
-    <row r="17" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7303,18 +7475,22 @@
       <c r="EB17" s="4"/>
       <c r="EC17" s="4"/>
       <c r="ED17" s="4"/>
+      <c r="EE17" s="4"/>
+      <c r="EF17" s="4"/>
+      <c r="EG17" s="4"/>
+      <c r="EH17" s="4"/>
     </row>
-    <row r="18" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -7716,18 +7892,30 @@
       <c r="ED18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -8129,18 +8317,30 @@
       <c r="ED19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="4"/>
@@ -8542,8 +8742,20 @@
       <c r="ED20" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH20" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -8789,17 +9001,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -9201,8 +9413,20 @@
       <c r="ED22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -9504,17 +9728,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -9916,8 +10140,20 @@
       <c r="ED24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -10273,18 +10509,22 @@
       <c r="EB25" s="4"/>
       <c r="EC25" s="4"/>
       <c r="ED25" s="4"/>
+      <c r="EE25" s="4"/>
+      <c r="EF25" s="4"/>
+      <c r="EG25" s="4"/>
+      <c r="EH25" s="4"/>
     </row>
-    <row r="26" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -10296,7 +10536,7 @@
       </c>
       <c r="F26" s="4">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="5"/>
@@ -10686,18 +10926,30 @@
       <c r="ED26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF26" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EG26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -11069,18 +11321,30 @@
       <c r="ED27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B28" s="4">
         <f t="shared" si="11"/>
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C28" s="4">
         <f t="shared" si="12"/>
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" si="13"/>
@@ -11386,18 +11650,30 @@
       <c r="ED28" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH28" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -11703,18 +11979,30 @@
       <c r="ED29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -11855,18 +12143,30 @@
       <c r="ED30" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH30" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -11878,7 +12178,7 @@
       </c>
       <c r="F31" s="4">
         <f t="shared" ref="F31" si="33">COUNTIF(K31:VT31,"B")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" ref="G31" si="34">COUNTIF(K31:VU31,"M")</f>
@@ -11971,18 +12271,30 @@
       <c r="ED31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EE31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG31" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EH31" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="32" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -12073,6 +12385,18 @@
         <v>32</v>
       </c>
       <c r="ED32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EE32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A7ABFB-CDC4-1843-B93A-B48F163359DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9E2699-547E-5A4D-BA45-DCC53382460B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3357" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:EH32"/>
+  <dimension ref="A1:EI32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:138" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:139" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,18 +1061,21 @@
       <c r="EH1" s="3">
         <v>46099</v>
       </c>
+      <c r="EI1" s="3">
+        <v>46101</v>
+      </c>
     </row>
-    <row r="2" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1486,14 +1489,17 @@
       <c r="EH2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -1517,7 +1523,7 @@
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H26" si="6">COUNTIF(K3:VV3,"R")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I26" si="7">COUNTIF(K3:VW3,"RH")</f>
@@ -1911,18 +1917,21 @@
       <c r="EH3" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI3" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2336,18 +2345,21 @@
       <c r="EH4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2761,14 +2773,17 @@
       <c r="EH5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
@@ -2792,7 +2807,7 @@
       </c>
       <c r="H6" s="4">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="7"/>
@@ -3186,18 +3201,21 @@
       <c r="EH6" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI6" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="7" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3209,7 +3227,7 @@
       </c>
       <c r="F7" s="4">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="5"/>
@@ -3603,26 +3621,29 @@
         <v>35</v>
       </c>
       <c r="EF7" s="4" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="EG7" s="4" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="EH7" s="4" t="s">
-        <v>35</v>
+        <v>7</v>
+      </c>
+      <c r="EI7" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" si="4"/>
@@ -4036,18 +4057,21 @@
       <c r="EH8" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI8" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4461,18 +4485,21 @@
       <c r="EH9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -4886,18 +4913,21 @@
       <c r="EH10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5311,8 +5341,11 @@
       <c r="EH11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5473,13 +5506,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -5495,7 +5528,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -5897,18 +5930,21 @@
       <c r="EH13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EI13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6322,18 +6358,21 @@
       <c r="EH14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -6747,8 +6786,11 @@
       <c r="EH15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -7120,8 +7162,9 @@
       <c r="EF16" s="4"/>
       <c r="EG16" s="4"/>
       <c r="EH16" s="4"/>
+      <c r="EI16" s="4"/>
     </row>
-    <row r="17" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7479,18 +7522,19 @@
       <c r="EF17" s="4"/>
       <c r="EG17" s="4"/>
       <c r="EH17" s="4"/>
+      <c r="EI17" s="4"/>
     </row>
-    <row r="18" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -7904,18 +7948,21 @@
       <c r="EH18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -8329,18 +8376,21 @@
       <c r="EH19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="4"/>
@@ -8754,8 +8804,11 @@
       <c r="EH20" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI20" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -9001,17 +9054,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -9425,8 +9478,11 @@
       <c r="EH22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -9728,17 +9784,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -10152,8 +10208,11 @@
       <c r="EH24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -10513,18 +10572,19 @@
       <c r="EF25" s="4"/>
       <c r="EG25" s="4"/>
       <c r="EH25" s="4"/>
+      <c r="EI25" s="4"/>
     </row>
-    <row r="26" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -10938,18 +10998,21 @@
       <c r="EH26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -11333,18 +11396,21 @@
       <c r="EH27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B28" s="4">
         <f t="shared" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" s="4">
         <f t="shared" si="12"/>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" si="13"/>
@@ -11662,18 +11728,21 @@
       <c r="EH28" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI28" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -11991,18 +12060,21 @@
       <c r="EH29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -12155,14 +12227,17 @@
       <c r="EH30" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EI30" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
@@ -12178,7 +12253,7 @@
       </c>
       <c r="F31" s="4">
         <f t="shared" ref="F31" si="33">COUNTIF(K31:VT31,"B")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" ref="G31" si="34">COUNTIF(K31:VU31,"M")</f>
@@ -12283,18 +12358,21 @@
       <c r="EH31" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EI31" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="32" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -12397,6 +12475,9 @@
         <v>7</v>
       </c>
       <c r="EH32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EI32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9E2699-547E-5A4D-BA45-DCC53382460B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2763A4-33A1-CB47-BC79-B53390CFCEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3430" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:EI32"/>
+  <dimension ref="A1:EK32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:139" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:141" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1064,18 +1064,24 @@
       <c r="EI1" s="3">
         <v>46101</v>
       </c>
+      <c r="EJ1" s="3">
+        <v>46105</v>
+      </c>
+      <c r="EK1" s="3">
+        <v>46106</v>
+      </c>
     </row>
-    <row r="2" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1492,14 +1498,20 @@
       <c r="EI2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -1519,7 +1531,7 @@
       </c>
       <c r="G3" s="4">
         <f t="shared" ref="G3:G26" si="5">COUNTIF(K3:VU3,"M")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H26" si="6">COUNTIF(K3:VV3,"R")</f>
@@ -1920,18 +1932,24 @@
       <c r="EI3" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="EJ3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="EK3" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="4" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2348,18 +2366,24 @@
       <c r="EI4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2776,18 +2800,24 @@
       <c r="EI5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="4"/>
@@ -3204,18 +3234,24 @@
       <c r="EI6" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="EJ6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK6" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3632,18 +3668,24 @@
       <c r="EI7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK7" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" si="4"/>
@@ -3655,7 +3697,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4058,20 +4100,26 @@
         <v>7</v>
       </c>
       <c r="EI8" s="4" t="s">
-        <v>7</v>
+        <v>35</v>
+      </c>
+      <c r="EJ8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EK8" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4488,18 +4536,24 @@
       <c r="EI9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -4916,18 +4970,24 @@
       <c r="EI10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5344,8 +5404,14 @@
       <c r="EI11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5506,13 +5572,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -5528,7 +5594,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -5933,18 +5999,24 @@
       <c r="EI13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EJ13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EK13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6361,18 +6433,24 @@
       <c r="EI14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -6789,8 +6867,14 @@
       <c r="EI15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -7163,8 +7247,10 @@
       <c r="EG16" s="4"/>
       <c r="EH16" s="4"/>
       <c r="EI16" s="4"/>
+      <c r="EJ16" s="4"/>
+      <c r="EK16" s="4"/>
     </row>
-    <row r="17" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7523,18 +7609,20 @@
       <c r="EG17" s="4"/>
       <c r="EH17" s="4"/>
       <c r="EI17" s="4"/>
+      <c r="EJ17" s="4"/>
+      <c r="EK17" s="4"/>
     </row>
-    <row r="18" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -7951,18 +8039,24 @@
       <c r="EI18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -8379,18 +8473,24 @@
       <c r="EI19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="4"/>
@@ -8807,8 +8907,14 @@
       <c r="EI20" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK20" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -9054,17 +9160,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -9481,8 +9587,14 @@
       <c r="EI22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -9784,17 +9896,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -10211,8 +10323,14 @@
       <c r="EI24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -10573,18 +10691,20 @@
       <c r="EG25" s="4"/>
       <c r="EH25" s="4"/>
       <c r="EI25" s="4"/>
+      <c r="EJ25" s="4"/>
+      <c r="EK25" s="4"/>
     </row>
-    <row r="26" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -11001,14 +11121,20 @@
       <c r="EI26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
@@ -11024,7 +11150,7 @@
       </c>
       <c r="F27" s="4">
         <f t="shared" ref="F27:F29" si="15">COUNTIF(K27:VT27,"B")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" ref="G27:G29" si="16">COUNTIF(K27:VU27,"M")</f>
@@ -11399,8 +11525,14 @@
       <c r="EI27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ27" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EK27" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="28" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -11731,18 +11863,20 @@
       <c r="EI28" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ28" s="4"/>
+      <c r="EK28" s="4"/>
     </row>
-    <row r="29" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -12063,14 +12197,20 @@
       <c r="EI29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -12090,7 +12230,7 @@
       </c>
       <c r="G30" s="4">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" ref="H30" si="26">COUNTIF(K30:VV30,"R")</f>
@@ -12230,18 +12370,24 @@
       <c r="EI30" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EJ30" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="EK30" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="31" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -12361,18 +12507,24 @@
       <c r="EI31" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EJ31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:139" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:141" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -12478,6 +12630,12 @@
         <v>7</v>
       </c>
       <c r="EI32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EJ32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2763A4-33A1-CB47-BC79-B53390CFCEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D180D972-93F9-A142-BE8A-8072FD04A592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3430" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3454" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:EK32"/>
+  <dimension ref="A1:EL32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:141" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:142" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1070,18 +1070,21 @@
       <c r="EK1" s="3">
         <v>46106</v>
       </c>
+      <c r="EL1" s="3">
+        <v>46108</v>
+      </c>
     </row>
-    <row r="2" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1504,14 +1507,17 @@
       <c r="EK2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -1535,7 +1541,7 @@
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H26" si="6">COUNTIF(K3:VV3,"R")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I26" si="7">COUNTIF(K3:VW3,"RH")</f>
@@ -1938,18 +1944,21 @@
       <c r="EK3" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="EL3" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2372,18 +2381,21 @@
       <c r="EK4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2806,14 +2818,17 @@
       <c r="EK5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
@@ -2837,7 +2852,7 @@
       </c>
       <c r="H6" s="4">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="7"/>
@@ -3240,18 +3255,21 @@
       <c r="EK6" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL6" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="7" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3674,14 +3692,17 @@
       <c r="EK7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL7" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -3697,7 +3718,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4108,18 +4129,21 @@
       <c r="EK8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EL8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4542,18 +4566,21 @@
       <c r="EK9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -4976,18 +5003,21 @@
       <c r="EK10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5410,8 +5440,11 @@
       <c r="EK11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5572,13 +5605,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -5594,7 +5627,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -6005,18 +6038,21 @@
       <c r="EK13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EL13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6439,18 +6475,21 @@
       <c r="EK14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -6873,8 +6912,11 @@
       <c r="EK15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -7249,8 +7291,9 @@
       <c r="EI16" s="4"/>
       <c r="EJ16" s="4"/>
       <c r="EK16" s="4"/>
+      <c r="EL16" s="4"/>
     </row>
-    <row r="17" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7611,18 +7654,19 @@
       <c r="EI17" s="4"/>
       <c r="EJ17" s="4"/>
       <c r="EK17" s="4"/>
+      <c r="EL17" s="4"/>
     </row>
-    <row r="18" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -8045,18 +8089,21 @@
       <c r="EK18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -8479,18 +8526,21 @@
       <c r="EK19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="4"/>
@@ -8913,8 +8963,11 @@
       <c r="EK20" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL20" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -9160,17 +9213,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -9593,8 +9646,11 @@
       <c r="EK22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -9896,17 +9952,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -10329,8 +10385,11 @@
       <c r="EK24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -10693,18 +10752,19 @@
       <c r="EI25" s="4"/>
       <c r="EJ25" s="4"/>
       <c r="EK25" s="4"/>
+      <c r="EL25" s="4"/>
     </row>
-    <row r="26" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -11127,14 +11187,17 @@
       <c r="EK26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
@@ -11150,7 +11213,7 @@
       </c>
       <c r="F27" s="4">
         <f t="shared" ref="F27:F29" si="15">COUNTIF(K27:VT27,"B")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" ref="G27:G29" si="16">COUNTIF(K27:VU27,"M")</f>
@@ -11531,8 +11594,11 @@
       <c r="EK27" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EL27" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="28" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -11865,18 +11931,19 @@
       </c>
       <c r="EJ28" s="4"/>
       <c r="EK28" s="4"/>
+      <c r="EL28" s="4"/>
     </row>
-    <row r="29" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -12203,18 +12270,21 @@
       <c r="EK29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -12376,18 +12446,21 @@
       <c r="EK30" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="EL30" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -12513,18 +12586,21 @@
       <c r="EK31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EL31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:141" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:142" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -12636,6 +12712,9 @@
         <v>7</v>
       </c>
       <c r="EK32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EL32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D180D972-93F9-A142-BE8A-8072FD04A592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50438425-5480-5D49-8D58-B96EA943EF3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3454" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3526" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:EL32"/>
+  <dimension ref="A1:EO32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:142" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:145" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1073,18 +1073,27 @@
       <c r="EL1" s="3">
         <v>46108</v>
       </c>
+      <c r="EM1" s="3">
+        <v>46112</v>
+      </c>
+      <c r="EN1" s="3">
+        <v>46113</v>
+      </c>
+      <c r="EO1" s="3">
+        <v>46115</v>
+      </c>
     </row>
-    <row r="2" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1510,18 +1519,27 @@
       <c r="EL2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="6">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1541,7 +1559,7 @@
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H26" si="6">COUNTIF(K3:VV3,"R")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I26" si="7">COUNTIF(K3:VW3,"RH")</f>
@@ -1947,18 +1965,27 @@
       <c r="EL3" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="EM3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO3" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -1966,7 +1993,7 @@
       </c>
       <c r="E4" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="1"/>
@@ -2384,18 +2411,27 @@
       <c r="EL4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="EN4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2821,14 +2857,23 @@
       <c r="EL5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
@@ -2844,7 +2889,7 @@
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(K6:VT6,"B")</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="5"/>
@@ -3258,18 +3303,27 @@
       <c r="EL6" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="EM6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EN6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EO6" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="7" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3695,14 +3749,23 @@
       <c r="EL7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO7" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -3718,7 +3781,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4132,18 +4195,27 @@
       <c r="EL8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EM8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EN8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EO8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4569,18 +4641,27 @@
       <c r="EL9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -5006,14 +5087,23 @@
       <c r="EL10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
@@ -5029,7 +5119,7 @@
       </c>
       <c r="F11" s="4">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" si="5"/>
@@ -5443,8 +5533,17 @@
       <c r="EL11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EN11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EO11" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="12" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5605,13 +5704,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -5627,7 +5726,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -6041,18 +6140,27 @@
       <c r="EL13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EM13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EN13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EO13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6478,18 +6586,27 @@
       <c r="EL14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -6915,8 +7032,17 @@
       <c r="EL15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -7292,8 +7418,11 @@
       <c r="EJ16" s="4"/>
       <c r="EK16" s="4"/>
       <c r="EL16" s="4"/>
+      <c r="EM16" s="4"/>
+      <c r="EN16" s="4"/>
+      <c r="EO16" s="4"/>
     </row>
-    <row r="17" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7655,18 +7784,21 @@
       <c r="EJ17" s="4"/>
       <c r="EK17" s="4"/>
       <c r="EL17" s="4"/>
+      <c r="EM17" s="4"/>
+      <c r="EN17" s="4"/>
+      <c r="EO17" s="4"/>
     </row>
-    <row r="18" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -8092,18 +8224,27 @@
       <c r="EL18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -8529,14 +8670,23 @@
       <c r="EL19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
@@ -8552,7 +8702,7 @@
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="5"/>
@@ -8966,8 +9116,17 @@
       <c r="EL20" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EN20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EO20" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="21" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -9213,17 +9372,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -9649,8 +9808,17 @@
       <c r="EL22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -9952,17 +10120,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -10388,8 +10556,17 @@
       <c r="EL24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -10753,18 +10930,21 @@
       <c r="EJ25" s="4"/>
       <c r="EK25" s="4"/>
       <c r="EL25" s="4"/>
+      <c r="EM25" s="4"/>
+      <c r="EN25" s="4"/>
+      <c r="EO25" s="4"/>
     </row>
-    <row r="26" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -11190,18 +11370,27 @@
       <c r="EL26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -11597,8 +11786,17 @@
       <c r="EL27" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EM27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -11932,18 +12130,21 @@
       <c r="EJ28" s="4"/>
       <c r="EK28" s="4"/>
       <c r="EL28" s="4"/>
+      <c r="EM28" s="4"/>
+      <c r="EN28" s="4"/>
+      <c r="EO28" s="4"/>
     </row>
-    <row r="29" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -12273,18 +12474,27 @@
       <c r="EL29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -12296,7 +12506,7 @@
       </c>
       <c r="F30" s="4">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -12449,18 +12659,27 @@
       <c r="EL30" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EO30" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="31" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -12589,18 +12808,27 @@
       <c r="EL31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EM31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:142" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:145" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -12715,6 +12943,15 @@
         <v>7</v>
       </c>
       <c r="EL32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EM32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50438425-5480-5D49-8D58-B96EA943EF3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6411AF-53A7-EF47-992D-8D1C1F410DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3526" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3550" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:EO32"/>
+  <dimension ref="A1:EP32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:145" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:146" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1082,18 +1082,21 @@
       <c r="EO1" s="3">
         <v>46115</v>
       </c>
+      <c r="EP1" s="3">
+        <v>46119</v>
+      </c>
     </row>
-    <row r="2" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1528,18 +1531,21 @@
       <c r="EO2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D3" s="6">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1974,18 +1980,21 @@
       <c r="EO3" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="EP3" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2420,18 +2429,21 @@
       <c r="EO4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2866,14 +2878,17 @@
       <c r="EO5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
@@ -2885,7 +2900,7 @@
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(K6:VT6,"B")</f>
@@ -3312,18 +3327,21 @@
       <c r="EO6" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EP6" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="7" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3758,14 +3776,17 @@
       <c r="EO7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP7" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -3781,7 +3802,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4204,18 +4225,21 @@
       <c r="EO8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EP8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4650,18 +4674,21 @@
       <c r="EO9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -5096,14 +5123,17 @@
       <c r="EO10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
@@ -5119,7 +5149,7 @@
       </c>
       <c r="F11" s="4">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" si="5"/>
@@ -5542,8 +5572,11 @@
       <c r="EO11" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EP11" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="12" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5704,17 +5737,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" s="6">
         <f t="shared" si="4"/>
@@ -6149,18 +6182,21 @@
       <c r="EO13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EP13" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6595,18 +6631,21 @@
       <c r="EO14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -7041,8 +7080,11 @@
       <c r="EO15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -7421,8 +7463,9 @@
       <c r="EM16" s="4"/>
       <c r="EN16" s="4"/>
       <c r="EO16" s="4"/>
+      <c r="EP16" s="4"/>
     </row>
-    <row r="17" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7787,18 +7830,19 @@
       <c r="EM17" s="4"/>
       <c r="EN17" s="4"/>
       <c r="EO17" s="4"/>
+      <c r="EP17" s="4"/>
     </row>
-    <row r="18" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -8233,18 +8277,21 @@
       <c r="EO18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -8679,14 +8726,17 @@
       <c r="EO19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
@@ -8702,7 +8752,7 @@
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="5"/>
@@ -9125,8 +9175,11 @@
       <c r="EO20" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EP20" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="21" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -9372,13 +9425,13 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
@@ -9386,7 +9439,7 @@
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
@@ -9817,8 +9870,11 @@
       <c r="EO22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP22" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="23" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -10120,17 +10176,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -10565,8 +10621,11 @@
       <c r="EO24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -10933,18 +10992,19 @@
       <c r="EM25" s="4"/>
       <c r="EN25" s="4"/>
       <c r="EO25" s="4"/>
+      <c r="EP25" s="4"/>
     </row>
-    <row r="26" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -11379,18 +11439,21 @@
       <c r="EO26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -11795,8 +11858,11 @@
       <c r="EO27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -12133,18 +12199,19 @@
       <c r="EM28" s="4"/>
       <c r="EN28" s="4"/>
       <c r="EO28" s="4"/>
+      <c r="EP28" s="4"/>
     </row>
-    <row r="29" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -12483,14 +12550,17 @@
       <c r="EO29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -12506,7 +12576,7 @@
       </c>
       <c r="F30" s="4">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -12668,18 +12738,21 @@
       <c r="EO30" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EP30" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="31" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -12817,18 +12890,21 @@
       <c r="EO31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EP31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:145" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:146" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -12952,6 +13028,9 @@
         <v>7</v>
       </c>
       <c r="EO32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EP32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6411AF-53A7-EF47-992D-8D1C1F410DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B942A32E-62F6-8343-9627-88C73D28F43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3550" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3598" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:EP32"/>
+  <dimension ref="A1:ER32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:146" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:148" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1085,18 +1085,24 @@
       <c r="EP1" s="3">
         <v>46119</v>
       </c>
+      <c r="EQ1" s="3">
+        <v>46120</v>
+      </c>
+      <c r="ER1" s="3">
+        <v>46122</v>
+      </c>
     </row>
-    <row r="2" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1534,14 +1540,20 @@
       <c r="EP2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -1553,7 +1565,7 @@
       </c>
       <c r="E3" s="4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="1"/>
@@ -1565,7 +1577,7 @@
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H26" si="6">COUNTIF(K3:VV3,"R")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I26" si="7">COUNTIF(K3:VW3,"RH")</f>
@@ -1983,18 +1995,24 @@
       <c r="EP3" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="ER3" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2432,18 +2450,24 @@
       <c r="EP4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2881,14 +2905,20 @@
       <c r="EP5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
@@ -2900,7 +2930,7 @@
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(K6:VT6,"B")</f>
@@ -3330,18 +3360,24 @@
       <c r="EP6" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="EQ6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="ER6" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="7" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3779,14 +3815,20 @@
       <c r="EP7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER7" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -3802,7 +3844,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4228,18 +4270,24 @@
       <c r="EP8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EQ8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="ER8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4677,18 +4725,24 @@
       <c r="EP9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -5126,18 +5180,24 @@
       <c r="EP10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5575,8 +5635,14 @@
       <c r="EP11" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EQ11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5737,21 +5803,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
@@ -6185,18 +6251,24 @@
       <c r="EP13" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER13" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="14" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6634,18 +6706,24 @@
       <c r="EP14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -7083,8 +7161,14 @@
       <c r="EP15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -7464,8 +7548,10 @@
       <c r="EN16" s="4"/>
       <c r="EO16" s="4"/>
       <c r="EP16" s="4"/>
+      <c r="EQ16" s="4"/>
+      <c r="ER16" s="4"/>
     </row>
-    <row r="17" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7831,18 +7917,20 @@
       <c r="EN17" s="4"/>
       <c r="EO17" s="4"/>
       <c r="EP17" s="4"/>
+      <c r="EQ17" s="4"/>
+      <c r="ER17" s="4"/>
     </row>
-    <row r="18" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -8280,18 +8368,24 @@
       <c r="EP18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -8729,14 +8823,20 @@
       <c r="EP19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
@@ -8752,7 +8852,7 @@
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="5"/>
@@ -9178,8 +9278,14 @@
       <c r="EP20" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EQ20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="ER20" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="21" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -9425,13 +9531,13 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
@@ -9439,7 +9545,7 @@
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
@@ -9873,8 +9979,14 @@
       <c r="EP22" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="EQ22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="ER22" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="23" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -10176,17 +10288,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -10624,8 +10736,14 @@
       <c r="EP24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -10993,18 +11111,20 @@
       <c r="EN25" s="4"/>
       <c r="EO25" s="4"/>
       <c r="EP25" s="4"/>
+      <c r="EQ25" s="4"/>
+      <c r="ER25" s="4"/>
     </row>
-    <row r="26" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -11442,22 +11562,28 @@
       <c r="EP26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" s="4">
         <f t="shared" ref="E27:E29" si="14">COUNTIF(K27:VS27,"A")</f>
@@ -11861,8 +11987,14 @@
       <c r="EP27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER27" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="28" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -12200,18 +12332,20 @@
       <c r="EN28" s="4"/>
       <c r="EO28" s="4"/>
       <c r="EP28" s="4"/>
+      <c r="EQ28" s="4"/>
+      <c r="ER28" s="4"/>
     </row>
-    <row r="29" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -12553,14 +12687,20 @@
       <c r="EP29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -12576,7 +12716,7 @@
       </c>
       <c r="F30" s="4">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -12741,18 +12881,24 @@
       <c r="EP30" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EQ30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="ER30" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="31" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -12893,18 +13039,24 @@
       <c r="EP31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EQ31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:146" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:148" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -13031,6 +13183,12 @@
         <v>7</v>
       </c>
       <c r="EP32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EQ32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B942A32E-62F6-8343-9627-88C73D28F43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4982E3E2-38CA-1A45-AB81-A3E84D6E57A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3598" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3670" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:ER32"/>
+  <dimension ref="A1:EU32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:148" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:151" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1091,18 +1091,27 @@
       <c r="ER1" s="3">
         <v>46122</v>
       </c>
+      <c r="ES1" s="3">
+        <v>46126</v>
+      </c>
+      <c r="ET1" s="3">
+        <v>46127</v>
+      </c>
+      <c r="EU1" s="3">
+        <v>46129</v>
+      </c>
     </row>
-    <row r="2" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1546,18 +1555,27 @@
       <c r="ER2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D3" s="6">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -2001,18 +2019,27 @@
       <c r="ER3" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="ES3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU3" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2456,18 +2483,27 @@
       <c r="ER4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2911,14 +2947,23 @@
       <c r="ER5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
@@ -2946,7 +2991,7 @@
       </c>
       <c r="I6" s="4">
         <f t="shared" si="7"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="8"/>
@@ -3366,18 +3411,27 @@
       <c r="ER6" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="ES6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="ET6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="EU6" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="7" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3821,14 +3875,23 @@
       <c r="ER7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU7" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -3844,7 +3907,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4276,18 +4339,27 @@
       <c r="ER8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="ES8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="ET8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EU8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4731,18 +4803,27 @@
       <c r="ER9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -5186,18 +5267,27 @@
       <c r="ER10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5641,8 +5731,17 @@
       <c r="ER11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5803,17 +5902,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="6">
         <f t="shared" si="4"/>
@@ -5825,7 +5924,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -6257,18 +6356,27 @@
       <c r="ER13" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="ES13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EU13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6712,18 +6820,27 @@
       <c r="ER14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -7167,8 +7284,17 @@
       <c r="ER15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -7550,8 +7676,11 @@
       <c r="EP16" s="4"/>
       <c r="EQ16" s="4"/>
       <c r="ER16" s="4"/>
+      <c r="ES16" s="4"/>
+      <c r="ET16" s="4"/>
+      <c r="EU16" s="4"/>
     </row>
-    <row r="17" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -7919,18 +8048,21 @@
       <c r="EP17" s="4"/>
       <c r="EQ17" s="4"/>
       <c r="ER17" s="4"/>
+      <c r="ES17" s="4"/>
+      <c r="ET17" s="4"/>
+      <c r="EU17" s="4"/>
     </row>
-    <row r="18" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -8374,18 +8506,27 @@
       <c r="ER18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -8829,14 +8970,23 @@
       <c r="ER19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
@@ -8852,7 +9002,7 @@
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="5"/>
@@ -9284,8 +9434,17 @@
       <c r="ER20" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="ES20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="ET20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EU20" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="21" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -9531,17 +9690,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -9985,8 +10144,17 @@
       <c r="ER22" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="ES22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -10288,17 +10456,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -10742,8 +10910,17 @@
       <c r="ER24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -11113,18 +11290,21 @@
       <c r="EP25" s="4"/>
       <c r="EQ25" s="4"/>
       <c r="ER25" s="4"/>
+      <c r="ES25" s="4"/>
+      <c r="ET25" s="4"/>
+      <c r="EU25" s="4"/>
     </row>
-    <row r="26" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -11568,14 +11748,23 @@
       <c r="ER26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
@@ -11583,7 +11772,7 @@
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E27" s="4">
         <f t="shared" ref="E27:E29" si="14">COUNTIF(K27:VS27,"A")</f>
@@ -11993,8 +12182,17 @@
       <c r="ER27" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="ES27" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="ET27" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="EU27" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="28" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -12334,18 +12532,21 @@
       <c r="EP28" s="4"/>
       <c r="EQ28" s="4"/>
       <c r="ER28" s="4"/>
+      <c r="ES28" s="4"/>
+      <c r="ET28" s="4"/>
+      <c r="EU28" s="4"/>
     </row>
-    <row r="29" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -12693,14 +12894,23 @@
       <c r="ER29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -12728,7 +12938,7 @@
       </c>
       <c r="I30" s="4">
         <f t="shared" ref="I30" si="27">COUNTIF(K30:VW30,"RH")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" ref="J30" si="28">COUNTIF(K30:VW30,"S")</f>
@@ -12887,18 +13097,27 @@
       <c r="ER30" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="ES30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="ET30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="EU30" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="31" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -13045,18 +13264,27 @@
       <c r="ER31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="ES31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:148" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:151" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -13068,7 +13296,7 @@
       </c>
       <c r="F32" s="4">
         <f t="shared" ref="F32" si="42">COUNTIF(K32:VT32,"B")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" ref="G32" si="43">COUNTIF(K32:VU32,"M")</f>
@@ -13190,6 +13418,15 @@
       </c>
       <c r="ER32" s="4" t="s">
         <v>7</v>
+      </c>
+      <c r="ES32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET32" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EU32" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4982E3E2-38CA-1A45-AB81-A3E84D6E57A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C86714E-D1DE-F34A-AE2A-FB49668AF22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3670" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:EU32"/>
+  <dimension ref="A1:EX32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:151" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:154" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1100,18 +1100,27 @@
       <c r="EU1" s="3">
         <v>46129</v>
       </c>
+      <c r="EV1" s="3">
+        <v>46133</v>
+      </c>
+      <c r="EW1" s="3">
+        <v>46134</v>
+      </c>
+      <c r="EX1" s="3">
+        <v>46136</v>
+      </c>
     </row>
-    <row r="2" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1564,18 +1573,27 @@
       <c r="EU2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D3" s="6">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1595,7 +1613,7 @@
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H26" si="6">COUNTIF(K3:VV3,"R")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I26" si="7">COUNTIF(K3:VW3,"RH")</f>
@@ -2028,18 +2046,27 @@
       <c r="EU3" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX3" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2492,18 +2519,27 @@
       <c r="EU4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2956,18 +2992,27 @@
       <c r="EU5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="4"/>
@@ -3420,18 +3465,27 @@
       <c r="EU6" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="EV6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX6" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
@@ -3884,14 +3938,23 @@
       <c r="EU7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX7" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -3907,7 +3970,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4348,18 +4411,27 @@
       <c r="EU8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EV8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EW8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EX8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4812,22 +4884,31 @@
       <c r="EU9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4">
         <f t="shared" si="0"/>
@@ -5276,18 +5357,27 @@
       <c r="EU10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="EX10" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="11" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5740,8 +5830,17 @@
       <c r="EU11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -5902,17 +6001,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="6">
         <f t="shared" si="4"/>
@@ -5924,7 +6023,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -6365,18 +6464,27 @@
       <c r="EU13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EV13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EX13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6829,22 +6937,31 @@
       <c r="EU14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
@@ -7293,8 +7410,17 @@
       <c r="EU15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="EW15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -7679,8 +7805,11 @@
       <c r="ES16" s="4"/>
       <c r="ET16" s="4"/>
       <c r="EU16" s="4"/>
+      <c r="EV16" s="4"/>
+      <c r="EW16" s="4"/>
+      <c r="EX16" s="4"/>
     </row>
-    <row r="17" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -8051,18 +8180,21 @@
       <c r="ES17" s="4"/>
       <c r="ET17" s="4"/>
       <c r="EU17" s="4"/>
+      <c r="EV17" s="4"/>
+      <c r="EW17" s="4"/>
+      <c r="EX17" s="4"/>
     </row>
-    <row r="18" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -8515,18 +8647,27 @@
       <c r="EU18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -8979,14 +9120,23 @@
       <c r="EU19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
@@ -9002,7 +9152,7 @@
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="5"/>
@@ -9443,8 +9593,17 @@
       <c r="EU20" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EV20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EW20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EX20" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="21" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -9690,17 +9849,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -10153,8 +10312,17 @@
       <c r="EU22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -10456,17 +10624,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -10919,8 +11087,17 @@
       <c r="EU24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -11293,18 +11470,21 @@
       <c r="ES25" s="4"/>
       <c r="ET25" s="4"/>
       <c r="EU25" s="4"/>
+      <c r="EV25" s="4"/>
+      <c r="EW25" s="4"/>
+      <c r="EX25" s="4"/>
     </row>
-    <row r="26" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -11757,22 +11937,31 @@
       <c r="EU26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E27" s="4">
         <f t="shared" ref="E27:E29" si="14">COUNTIF(K27:VS27,"A")</f>
@@ -11780,7 +11969,7 @@
       </c>
       <c r="F27" s="4">
         <f t="shared" ref="F27:F29" si="15">COUNTIF(K27:VT27,"B")</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" ref="G27:G29" si="16">COUNTIF(K27:VU27,"M")</f>
@@ -12186,13 +12375,22 @@
         <v>42</v>
       </c>
       <c r="ET27" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="EU27" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
+      </c>
+      <c r="EV27" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EW27" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EX27" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -12535,18 +12733,21 @@
       <c r="ES28" s="4"/>
       <c r="ET28" s="4"/>
       <c r="EU28" s="4"/>
+      <c r="EV28" s="4"/>
+      <c r="EW28" s="4"/>
+      <c r="EX28" s="4"/>
     </row>
-    <row r="29" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -12903,14 +13104,23 @@
       <c r="EU29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -12938,7 +13148,7 @@
       </c>
       <c r="I30" s="4">
         <f t="shared" ref="I30" si="27">COUNTIF(K30:VW30,"RH")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" ref="J30" si="28">COUNTIF(K30:VW30,"S")</f>
@@ -13106,14 +13316,23 @@
       <c r="EU30" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="EV30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="EW30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="EX30" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="31" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
@@ -13129,7 +13348,7 @@
       </c>
       <c r="F31" s="4">
         <f t="shared" ref="F31" si="33">COUNTIF(K31:VT31,"B")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" ref="G31" si="34">COUNTIF(K31:VU31,"M")</f>
@@ -13273,18 +13492,27 @@
       <c r="EU31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EV31" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EW31" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EX31" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="32" spans="1:151" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:154" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -13292,7 +13520,7 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" ref="E32" si="41">COUNTIF(K32:VS32,"A")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" ref="F32" si="42">COUNTIF(K32:VT32,"B")</f>
@@ -13427,6 +13655,15 @@
       </c>
       <c r="EU32" s="4" t="s">
         <v>35</v>
+      </c>
+      <c r="EV32" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="EW32" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="EX32" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C86714E-D1DE-F34A-AE2A-FB49668AF22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49E2EDE-D93A-9943-9316-5042A999BA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:EX32"/>
+  <dimension ref="A1:EZ32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:154" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:156" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1109,18 +1109,24 @@
       <c r="EX1" s="3">
         <v>46136</v>
       </c>
+      <c r="EY1" s="3">
+        <v>46140</v>
+      </c>
+      <c r="EZ1" s="3">
+        <v>46141</v>
+      </c>
     </row>
-    <row r="2" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1582,14 +1588,20 @@
       <c r="EX2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -1605,7 +1617,7 @@
       </c>
       <c r="F3" s="4">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" ref="G3:G26" si="5">COUNTIF(K3:VU3,"M")</f>
@@ -2055,18 +2067,24 @@
       <c r="EX3" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="EY3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EZ3" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="4" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2528,18 +2546,24 @@
       <c r="EX4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -3001,18 +3025,24 @@
       <c r="EX5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="4"/>
@@ -3474,14 +3504,20 @@
       <c r="EX6" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ6" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
@@ -3489,7 +3525,7 @@
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4">
         <f>COUNTIF(K7:VS7,"A")</f>
@@ -3947,14 +3983,20 @@
       <c r="EX7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="EZ7" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="8" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -3970,7 +4012,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4420,18 +4462,24 @@
       <c r="EX8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EY8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EZ8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4893,14 +4941,20 @@
       <c r="EX9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
@@ -4908,7 +4962,7 @@
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" s="4">
         <f t="shared" si="0"/>
@@ -5366,18 +5420,24 @@
       <c r="EX10" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="EY10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="EZ10" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="11" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5839,8 +5899,14 @@
       <c r="EX11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -6001,13 +6067,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -6023,7 +6089,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -6473,18 +6539,24 @@
       <c r="EX13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EY13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EZ13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -6946,14 +7018,20 @@
       <c r="EX14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
@@ -6961,7 +7039,7 @@
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
@@ -7419,8 +7497,14 @@
       <c r="EX15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="EZ15" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="16" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -7808,8 +7892,10 @@
       <c r="EV16" s="4"/>
       <c r="EW16" s="4"/>
       <c r="EX16" s="4"/>
+      <c r="EY16" s="4"/>
+      <c r="EZ16" s="4"/>
     </row>
-    <row r="17" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -8183,14 +8269,16 @@
       <c r="EV17" s="4"/>
       <c r="EW17" s="4"/>
       <c r="EX17" s="4"/>
+      <c r="EY17" s="4"/>
+      <c r="EZ17" s="4"/>
     </row>
-    <row r="18" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
@@ -8206,7 +8294,7 @@
       </c>
       <c r="F18" s="4">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="5"/>
@@ -8656,18 +8744,24 @@
       <c r="EX18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EZ18" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="19" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -9129,14 +9223,20 @@
       <c r="EX19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
@@ -9152,7 +9252,7 @@
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="5"/>
@@ -9602,8 +9702,14 @@
       <c r="EX20" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EY20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EZ20" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="21" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -9849,17 +9955,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -10321,8 +10427,14 @@
       <c r="EX22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -10624,13 +10736,13 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
@@ -10638,7 +10750,7 @@
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="4">
         <f t="shared" si="0"/>
@@ -11096,8 +11208,14 @@
       <c r="EX24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="EZ24" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="25" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -11473,18 +11591,20 @@
       <c r="EV25" s="4"/>
       <c r="EW25" s="4"/>
       <c r="EX25" s="4"/>
+      <c r="EY25" s="4"/>
+      <c r="EZ25" s="4"/>
     </row>
-    <row r="26" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -11946,18 +12066,24 @@
       <c r="EX26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -12389,8 +12515,14 @@
       <c r="EX27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -12736,18 +12868,20 @@
       <c r="EV28" s="4"/>
       <c r="EW28" s="4"/>
       <c r="EX28" s="4"/>
+      <c r="EY28" s="4"/>
+      <c r="EZ28" s="4"/>
     </row>
-    <row r="29" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -13113,18 +13247,24 @@
       <c r="EX29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="EY29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -13136,7 +13276,7 @@
       </c>
       <c r="F30" s="4">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -13325,14 +13465,20 @@
       <c r="EX30" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="EY30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ30" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="31" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
@@ -13348,7 +13494,7 @@
       </c>
       <c r="F31" s="4">
         <f t="shared" ref="F31" si="33">COUNTIF(K31:VT31,"B")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" ref="G31" si="34">COUNTIF(K31:VU31,"M")</f>
@@ -13501,18 +13647,24 @@
       <c r="EX31" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="EY31" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="EZ31" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="32" spans="1:154" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:156" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -13663,6 +13815,12 @@
         <v>32</v>
       </c>
       <c r="EX32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EY32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49E2EDE-D93A-9943-9316-5042A999BA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CB0186-85B2-C140-991D-1F9DF034AD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:EZ32"/>
+  <dimension ref="A1:FC32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:156" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:159" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1115,18 +1115,27 @@
       <c r="EZ1" s="3">
         <v>46141</v>
       </c>
+      <c r="FA1" s="3">
+        <v>46142</v>
+      </c>
+      <c r="FB1" s="5">
+        <v>46146</v>
+      </c>
+      <c r="FC1" s="5">
+        <v>46147</v>
+      </c>
     </row>
-    <row r="2" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1594,14 +1603,23 @@
       <c r="EZ2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FA2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -1617,7 +1635,7 @@
       </c>
       <c r="F3" s="4">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" ref="G3:G26" si="5">COUNTIF(K3:VU3,"M")</f>
@@ -2073,18 +2091,27 @@
       <c r="EZ3" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FA3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FB3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FC3" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="4" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2552,18 +2579,27 @@
       <c r="EZ4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FA4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="4"/>
@@ -2575,7 +2611,7 @@
       </c>
       <c r="F5" s="4">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="5"/>
@@ -3026,23 +3062,32 @@
         <v>7</v>
       </c>
       <c r="EY5" s="4" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="EZ5" s="4" t="s">
-        <v>7</v>
+        <v>35</v>
+      </c>
+      <c r="FA5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FB5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FC5" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="4"/>
@@ -3050,7 +3095,7 @@
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(K6:VT6,"B")</f>
@@ -3510,22 +3555,31 @@
       <c r="EZ6" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FA6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="FC6" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="4">
         <f>COUNTIF(K7:VS7,"A")</f>
@@ -3989,14 +4043,23 @@
       <c r="EZ7" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="FA7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="FB7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC7" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -4012,7 +4075,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4468,18 +4531,27 @@
       <c r="EZ8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FA8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FB8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FC8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -4947,22 +5019,31 @@
       <c r="EZ9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FA9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4">
         <f t="shared" si="0"/>
@@ -5426,18 +5507,27 @@
       <c r="EZ10" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="FA10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="FB10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5905,8 +5995,17 @@
       <c r="EZ11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FA11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -6067,13 +6166,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -6089,7 +6188,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -6545,18 +6644,27 @@
       <c r="EZ13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FA13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FB13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FC13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -7024,22 +7132,31 @@
       <c r="EZ14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FA14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
@@ -7503,8 +7620,17 @@
       <c r="EZ15" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="FA15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="FB15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -7894,8 +8020,11 @@
       <c r="EX16" s="4"/>
       <c r="EY16" s="4"/>
       <c r="EZ16" s="4"/>
+      <c r="FA16" s="4"/>
+      <c r="FB16" s="4"/>
+      <c r="FC16" s="4"/>
     </row>
-    <row r="17" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -8271,14 +8400,17 @@
       <c r="EX17" s="4"/>
       <c r="EY17" s="4"/>
       <c r="EZ17" s="4"/>
+      <c r="FA17" s="4"/>
+      <c r="FB17" s="4"/>
+      <c r="FC17" s="4"/>
     </row>
-    <row r="18" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
@@ -8294,7 +8426,7 @@
       </c>
       <c r="F18" s="4">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="5"/>
@@ -8750,18 +8882,27 @@
       <c r="EZ18" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FA18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FB18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FC18" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="19" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -9229,14 +9370,23 @@
       <c r="EZ19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FA19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
@@ -9252,7 +9402,7 @@
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="5"/>
@@ -9708,8 +9858,17 @@
       <c r="EZ20" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FA20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FB20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FC20" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="21" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -9955,17 +10114,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -10433,8 +10592,17 @@
       <c r="EZ22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FA22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -10736,17 +10904,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -11214,8 +11382,17 @@
       <c r="EZ24" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="FA24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -11593,18 +11770,21 @@
       <c r="EX25" s="4"/>
       <c r="EY25" s="4"/>
       <c r="EZ25" s="4"/>
+      <c r="FA25" s="4"/>
+      <c r="FB25" s="4"/>
+      <c r="FC25" s="4"/>
     </row>
-    <row r="26" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -12072,18 +12252,27 @@
       <c r="EZ26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FA26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -12521,8 +12710,17 @@
       <c r="EZ27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FA27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -12870,18 +13068,21 @@
       <c r="EX28" s="4"/>
       <c r="EY28" s="4"/>
       <c r="EZ28" s="4"/>
+      <c r="FA28" s="4"/>
+      <c r="FB28" s="4"/>
+      <c r="FC28" s="4"/>
     </row>
-    <row r="29" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -13253,14 +13454,23 @@
       <c r="EZ29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FA29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -13276,7 +13486,7 @@
       </c>
       <c r="F30" s="4">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -13471,18 +13681,27 @@
       <c r="EZ30" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FA30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FB30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FC30" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="31" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -13494,7 +13713,7 @@
       </c>
       <c r="F31" s="4">
         <f t="shared" ref="F31" si="33">COUNTIF(K31:VT31,"B")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" ref="G31" si="34">COUNTIF(K31:VU31,"M")</f>
@@ -13653,18 +13872,27 @@
       <c r="EZ31" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FA31" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FB31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:156" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:159" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -13821,6 +14049,15 @@
         <v>7</v>
       </c>
       <c r="EZ32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FA32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CB0186-85B2-C140-991D-1F9DF034AD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70B56E4-7311-F14D-90D9-C83709C50FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3934" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:FC32"/>
+  <dimension ref="A1:FF32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:159" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:162" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1124,18 +1124,27 @@
       <c r="FC1" s="5">
         <v>46147</v>
       </c>
+      <c r="FD1" s="5">
+        <v>46148</v>
+      </c>
+      <c r="FE1" s="5">
+        <v>46150</v>
+      </c>
+      <c r="FF1" s="5">
+        <v>46154</v>
+      </c>
     </row>
-    <row r="2" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1612,18 +1621,27 @@
       <c r="FC2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D3" s="6">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1635,7 +1653,7 @@
       </c>
       <c r="F3" s="4">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" ref="G3:G26" si="5">COUNTIF(K3:VU3,"M")</f>
@@ -2095,23 +2113,32 @@
         <v>35</v>
       </c>
       <c r="FB3" s="4" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="FC3" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FD3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FE3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FF3" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="4" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2588,14 +2615,23 @@
       <c r="FC4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
@@ -2611,7 +2647,7 @@
       </c>
       <c r="F5" s="4">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="5"/>
@@ -3076,18 +3112,27 @@
       <c r="FC5" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FD5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FE5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FF5" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="6" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="4"/>
@@ -3095,7 +3140,7 @@
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(K6:VT6,"B")</f>
@@ -3564,22 +3609,31 @@
       <c r="FC6" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF6" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="7" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4">
         <f>COUNTIF(K7:VS7,"A")</f>
@@ -4052,14 +4106,23 @@
       <c r="FC7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF7" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="8" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -4075,7 +4138,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4540,18 +4603,27 @@
       <c r="FC8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FD8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FE8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FF8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -5028,18 +5100,27 @@
       <c r="FC9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -5516,18 +5597,27 @@
       <c r="FC10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -5543,7 +5633,7 @@
       </c>
       <c r="G11" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4">
         <f t="shared" si="6"/>
@@ -6004,8 +6094,17 @@
       <c r="FC11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF11" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="12" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -6166,13 +6265,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -6188,7 +6287,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -6653,18 +6752,27 @@
       <c r="FC13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FD13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FE13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FF13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -7141,18 +7249,27 @@
       <c r="FC14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -7629,8 +7746,17 @@
       <c r="FC15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -8023,8 +8149,11 @@
       <c r="FA16" s="4"/>
       <c r="FB16" s="4"/>
       <c r="FC16" s="4"/>
+      <c r="FD16" s="4"/>
+      <c r="FE16" s="4"/>
+      <c r="FF16" s="4"/>
     </row>
-    <row r="17" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -8403,14 +8532,17 @@
       <c r="FA17" s="4"/>
       <c r="FB17" s="4"/>
       <c r="FC17" s="4"/>
+      <c r="FD17" s="4"/>
+      <c r="FE17" s="4"/>
+      <c r="FF17" s="4"/>
     </row>
-    <row r="18" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
@@ -8426,7 +8558,7 @@
       </c>
       <c r="F18" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="5"/>
@@ -8891,18 +9023,27 @@
       <c r="FC18" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FD18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FE18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FF18" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="19" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -9379,14 +9520,23 @@
       <c r="FC19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
@@ -9402,7 +9552,7 @@
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="5"/>
@@ -9867,8 +10017,17 @@
       <c r="FC20" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FD20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FE20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FF20" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="21" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -10114,17 +10273,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -10601,8 +10760,17 @@
       <c r="FC22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -10904,17 +11072,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -11391,8 +11559,17 @@
       <c r="FC24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -11773,18 +11950,21 @@
       <c r="FA25" s="4"/>
       <c r="FB25" s="4"/>
       <c r="FC25" s="4"/>
+      <c r="FD25" s="4"/>
+      <c r="FE25" s="4"/>
+      <c r="FF25" s="4"/>
     </row>
-    <row r="26" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -12261,18 +12441,27 @@
       <c r="FC26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -12719,8 +12908,17 @@
       <c r="FC27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -13071,18 +13269,21 @@
       <c r="FA28" s="4"/>
       <c r="FB28" s="4"/>
       <c r="FC28" s="4"/>
+      <c r="FD28" s="4"/>
+      <c r="FE28" s="4"/>
+      <c r="FF28" s="4"/>
     </row>
-    <row r="29" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -13463,14 +13664,23 @@
       <c r="FC29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -13486,7 +13696,7 @@
       </c>
       <c r="F30" s="4">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -13690,22 +13900,31 @@
       <c r="FC30" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FD30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FE30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="FF30" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="31" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="4">
         <f t="shared" ref="E31" si="32">COUNTIF(K31:VS31,"A")</f>
@@ -13881,18 +14100,27 @@
       <c r="FC31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FD31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF31" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="32" spans="1:159" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:162" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -14058,6 +14286,15 @@
         <v>7</v>
       </c>
       <c r="FC32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FD32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70B56E4-7311-F14D-90D9-C83709C50FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9024803B-597E-644F-A986-B5EDFE15BE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3934" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3958" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:FF32"/>
+  <dimension ref="A1:FG32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:162" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:163" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1133,18 +1133,21 @@
       <c r="FF1" s="5">
         <v>46154</v>
       </c>
+      <c r="FG1" s="5">
+        <v>46155</v>
+      </c>
     </row>
-    <row r="2" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1630,14 +1633,17 @@
       <c r="FF2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -1653,7 +1659,7 @@
       </c>
       <c r="F3" s="4">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" ref="G3:G26" si="5">COUNTIF(K3:VU3,"M")</f>
@@ -2127,18 +2133,21 @@
       <c r="FF3" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FG3" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="4" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2624,14 +2633,17 @@
       <c r="FF4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
@@ -2647,7 +2659,7 @@
       </c>
       <c r="F5" s="4">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="5"/>
@@ -3121,14 +3133,17 @@
       <c r="FF5" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FG5" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="6" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
@@ -3140,7 +3155,7 @@
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(K6:VT6,"B")</f>
@@ -3618,14 +3633,17 @@
       <c r="FF6" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="FG6" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="7" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
@@ -3633,7 +3651,7 @@
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="4">
         <f>COUNTIF(K7:VS7,"A")</f>
@@ -4115,14 +4133,17 @@
       <c r="FF7" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="FG7" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="8" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -4138,7 +4159,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4612,18 +4633,21 @@
       <c r="FF8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FG8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -5109,18 +5133,21 @@
       <c r="FF9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -5606,18 +5633,21 @@
       <c r="FF10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -6103,8 +6133,11 @@
       <c r="FF11" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="FG11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -6265,13 +6298,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -6287,7 +6320,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -6761,18 +6794,21 @@
       <c r="FF13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FG13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -7258,18 +7294,21 @@
       <c r="FF14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -7755,8 +7794,11 @@
       <c r="FF15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -8152,8 +8194,9 @@
       <c r="FD16" s="4"/>
       <c r="FE16" s="4"/>
       <c r="FF16" s="4"/>
+      <c r="FG16" s="4"/>
     </row>
-    <row r="17" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -8535,18 +8578,19 @@
       <c r="FD17" s="4"/>
       <c r="FE17" s="4"/>
       <c r="FF17" s="4"/>
+      <c r="FG17" s="4"/>
     </row>
-    <row r="18" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -8558,7 +8602,7 @@
       </c>
       <c r="F18" s="4">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="5"/>
@@ -9024,26 +9068,29 @@
         <v>35</v>
       </c>
       <c r="FD18" s="4" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="FE18" s="4" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="FF18" s="4" t="s">
-        <v>35</v>
+        <v>7</v>
+      </c>
+      <c r="FG18" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -9529,14 +9576,17 @@
       <c r="FF19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
@@ -9552,7 +9602,7 @@
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="5"/>
@@ -10026,8 +10076,11 @@
       <c r="FF20" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FG20" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="21" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -10273,17 +10326,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -10769,8 +10822,11 @@
       <c r="FF22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -11072,17 +11128,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -11568,8 +11624,11 @@
       <c r="FF24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -11953,18 +12012,19 @@
       <c r="FD25" s="4"/>
       <c r="FE25" s="4"/>
       <c r="FF25" s="4"/>
+      <c r="FG25" s="4"/>
     </row>
-    <row r="26" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -12450,18 +12510,21 @@
       <c r="FF26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -12917,8 +12980,11 @@
       <c r="FF27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -13272,18 +13338,19 @@
       <c r="FD28" s="4"/>
       <c r="FE28" s="4"/>
       <c r="FF28" s="4"/>
+      <c r="FG28" s="4"/>
     </row>
-    <row r="29" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -13673,14 +13740,17 @@
       <c r="FF29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FG29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -13696,7 +13766,7 @@
       </c>
       <c r="F30" s="4">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -13909,18 +13979,21 @@
       <c r="FF30" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FG30" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="31" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -14109,18 +14182,21 @@
       <c r="FF31" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="FG31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:162" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:163" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -14295,6 +14371,9 @@
         <v>7</v>
       </c>
       <c r="FF32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FG32" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/Présences.xlsx
+++ b/data/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9024803B-597E-644F-A986-B5EDFE15BE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDCED616-E87A-2446-B30D-701E275092AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3958" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3982" uniqueCount="49">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -640,13 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:FG32"/>
+  <dimension ref="A1:FH32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:163" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:164" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1136,18 +1136,21 @@
       <c r="FG1" s="5">
         <v>46155</v>
       </c>
+      <c r="FH1" s="5">
+        <v>46157</v>
+      </c>
     </row>
-    <row r="2" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTA(K2:VR2)</f>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D2" s="6">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1636,14 +1639,17 @@
       <c r="FG2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -1667,7 +1673,7 @@
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H26" si="6">COUNTIF(K3:VV3,"R")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I26" si="7">COUNTIF(K3:VW3,"RH")</f>
@@ -2136,18 +2142,21 @@
       <c r="FG3" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FH3" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="4"/>
@@ -2636,14 +2645,17 @@
       <c r="FG4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
@@ -2659,7 +2671,7 @@
       </c>
       <c r="F5" s="4">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="5"/>
@@ -3136,14 +3148,17 @@
       <c r="FG5" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FH5" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="6" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
@@ -3155,7 +3170,7 @@
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(K6:VT6,"B")</f>
@@ -3636,14 +3651,17 @@
       <c r="FG6" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="FH6" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="7" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
@@ -3651,7 +3669,7 @@
       </c>
       <c r="D7" s="6">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" s="4">
         <f>COUNTIF(K7:VS7,"A")</f>
@@ -4136,14 +4154,17 @@
       <c r="FG7" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="FH7" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="8" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
@@ -4159,7 +4180,7 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="5"/>
@@ -4636,18 +4657,21 @@
       <c r="FG8" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FH8" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="4"/>
@@ -5136,18 +5160,21 @@
       <c r="FG9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="4"/>
@@ -5636,18 +5663,21 @@
       <c r="FG10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH10" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="4"/>
@@ -6136,8 +6166,11 @@
       <c r="FG11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -6298,13 +6331,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
@@ -6320,7 +6353,7 @@
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="5"/>
@@ -6797,18 +6830,21 @@
       <c r="FG13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FH13" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="4"/>
@@ -7297,18 +7333,21 @@
       <c r="FG14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH14" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="4"/>
@@ -7797,8 +7836,11 @@
       <c r="FG15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH15" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -8195,8 +8237,9 @@
       <c r="FE16" s="4"/>
       <c r="FF16" s="4"/>
       <c r="FG16" s="4"/>
+      <c r="FH16" s="4"/>
     </row>
-    <row r="17" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -8579,18 +8622,19 @@
       <c r="FE17" s="4"/>
       <c r="FF17" s="4"/>
       <c r="FG17" s="4"/>
+      <c r="FH17" s="4"/>
     </row>
-    <row r="18" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="4"/>
@@ -9079,18 +9123,21 @@
       <c r="FG18" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH18" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="4"/>
@@ -9579,14 +9626,17 @@
       <c r="FG19" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH19" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
@@ -9602,7 +9652,7 @@
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="5"/>
@@ -10079,8 +10129,11 @@
       <c r="FG20" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FH20" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="21" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -10326,17 +10379,17 @@
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
     </row>
-    <row r="22" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="4"/>
@@ -10825,8 +10878,11 @@
       <c r="FG22" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -11128,17 +11184,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="9"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="10"/>
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="4"/>
@@ -11627,8 +11683,11 @@
       <c r="FG24" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -12013,18 +12072,19 @@
       <c r="FE25" s="4"/>
       <c r="FF25" s="4"/>
       <c r="FG25" s="4"/>
+      <c r="FH25" s="4"/>
     </row>
-    <row r="26" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="9"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="10"/>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="4"/>
@@ -12513,18 +12573,21 @@
       <c r="FG26" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH26" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -12983,8 +13046,11 @@
       <c r="FG27" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH27" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
@@ -13339,18 +13405,19 @@
       <c r="FE28" s="4"/>
       <c r="FF28" s="4"/>
       <c r="FG28" s="4"/>
+      <c r="FH28" s="4"/>
     </row>
-    <row r="29" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="11"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="12"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="13"/>
@@ -13743,14 +13810,17 @@
       <c r="FG29" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH29" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -13766,7 +13836,7 @@
       </c>
       <c r="F30" s="4">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -13982,18 +14052,21 @@
       <c r="FG30" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="FH30" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="31" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -14185,18 +14258,21 @@
       <c r="FG31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="FH31" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:164" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -14374,6 +14450,9 @@
         <v>7</v>
       </c>
       <c r="FG32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="FH32" s="4" t="s">
         <v>7</v>
       </c>
     </row>
